--- a/panchang-data/NageshwarSaurashtra2026.xlsx
+++ b/panchang-data/NageshwarSaurashtra2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5405">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16240,6 +16240,9 @@
   </si>
   <si>
     <t>121°05'00.47</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16729,7 +16732,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16815,7 +16818,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
@@ -16901,7 +16904,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16987,7 +16990,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -17073,7 +17076,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17159,7 +17162,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>126</v>
@@ -17245,7 +17248,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>144</v>
@@ -17331,7 +17334,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17417,7 +17420,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>51</v>
@@ -17503,7 +17506,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17589,7 +17592,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17675,7 +17678,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17761,7 +17764,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>126</v>
@@ -17847,7 +17850,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>144</v>
@@ -17933,7 +17936,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18019,7 +18022,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>51</v>
@@ -18105,7 +18108,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18191,7 +18194,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18277,7 +18280,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18363,7 +18366,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>126</v>
@@ -18449,7 +18452,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>144</v>
@@ -18535,7 +18538,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18621,7 +18624,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>51</v>
@@ -18707,7 +18710,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18793,7 +18796,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18879,7 +18882,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18965,7 +18968,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>126</v>
@@ -19051,7 +19054,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>144</v>
@@ -19137,7 +19140,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19223,7 +19226,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>51</v>
@@ -19309,7 +19312,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19395,7 +19398,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>567</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19481,7 +19484,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19567,7 +19570,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>126</v>
@@ -19653,7 +19656,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>144</v>
@@ -19739,7 +19742,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19825,7 +19828,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>51</v>
@@ -19911,7 +19914,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19997,7 +20000,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -20083,7 +20086,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20169,7 +20172,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>126</v>
@@ -20255,7 +20258,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>144</v>
@@ -20341,7 +20344,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20427,7 +20430,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>51</v>
@@ -20513,7 +20516,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20599,7 +20602,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20685,7 +20688,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20771,7 +20774,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>126</v>
@@ -20857,7 +20860,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>144</v>
@@ -20943,7 +20946,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21029,7 +21032,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>51</v>
@@ -21115,7 +21118,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21201,7 +21204,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21287,7 +21290,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21373,7 +21376,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>126</v>
@@ -21459,7 +21462,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>144</v>
@@ -21545,7 +21548,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21631,7 +21634,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>51</v>
@@ -21717,7 +21720,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21803,7 +21806,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21889,7 +21892,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21975,7 +21978,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>567</v>
+        <v>1010</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>126</v>
@@ -22061,7 +22064,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>144</v>
@@ -22147,7 +22150,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22233,7 +22236,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>51</v>
@@ -22319,7 +22322,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22405,7 +22408,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22491,7 +22494,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22577,7 +22580,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>126</v>
@@ -22663,7 +22666,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>144</v>
@@ -22749,7 +22752,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22835,7 +22838,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>51</v>
@@ -22921,7 +22924,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -23007,7 +23010,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -23093,7 +23096,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23179,7 +23182,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>126</v>
@@ -23265,7 +23268,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>144</v>
@@ -23351,7 +23354,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23437,7 +23440,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>51</v>
@@ -23523,7 +23526,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23609,7 +23612,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23695,7 +23698,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23781,7 +23784,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>126</v>
@@ -23867,7 +23870,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>144</v>
@@ -23953,7 +23956,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24039,7 +24042,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>51</v>
@@ -24125,7 +24128,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24211,7 +24214,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24297,7 +24300,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24383,7 +24386,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>126</v>
@@ -24469,7 +24472,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1010</v>
+        <v>1438</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>144</v>
@@ -24555,7 +24558,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24641,7 +24644,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>51</v>
@@ -24727,7 +24730,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24813,7 +24816,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24899,7 +24902,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24985,7 +24988,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>126</v>
@@ -25071,7 +25074,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>144</v>
@@ -25157,7 +25160,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25243,7 +25246,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>51</v>
@@ -25329,7 +25332,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25415,7 +25418,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25501,7 +25504,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25587,7 +25590,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>126</v>
@@ -25673,7 +25676,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>144</v>
@@ -25759,7 +25762,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25845,7 +25848,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>51</v>
@@ -25931,7 +25934,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26017,7 +26020,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -26103,7 +26106,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26189,7 +26192,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>126</v>
@@ -26275,7 +26278,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>144</v>
@@ -26361,7 +26364,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26447,7 +26450,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>51</v>
@@ -26533,7 +26536,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26619,7 +26622,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26705,7 +26708,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26791,7 +26794,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>126</v>
@@ -26877,7 +26880,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>144</v>
@@ -26963,7 +26966,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27049,7 +27052,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1438</v>
+        <v>1875</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>51</v>
@@ -27135,7 +27138,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27221,7 +27224,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27307,7 +27310,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27393,7 +27396,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>126</v>
@@ -27479,7 +27482,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>144</v>
@@ -27565,7 +27568,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27651,7 +27654,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>51</v>
@@ -27737,7 +27740,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27823,7 +27826,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27909,7 +27912,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27995,7 +27998,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>126</v>
@@ -28081,7 +28084,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>144</v>
@@ -28167,7 +28170,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28253,7 +28256,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>51</v>
@@ -28339,7 +28342,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1875</v>
+        <v>2312</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28425,7 +28428,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28511,7 +28514,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28597,7 +28600,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>126</v>
@@ -28683,7 +28686,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>144</v>
@@ -28769,7 +28772,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28855,7 +28858,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>51</v>
@@ -28941,7 +28944,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29027,7 +29030,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -29113,7 +29116,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29199,7 +29202,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>126</v>
@@ -29285,7 +29288,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>144</v>
@@ -29371,7 +29374,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29457,7 +29460,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>51</v>
@@ -29543,7 +29546,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29629,7 +29632,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1875</v>
+        <v>5404</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29715,7 +29718,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29801,7 +29804,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>126</v>
@@ -29887,7 +29890,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>144</v>
@@ -29973,7 +29976,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30059,7 +30062,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>51</v>
@@ -30145,7 +30148,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30231,7 +30234,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30317,7 +30320,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30403,7 +30406,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>126</v>
@@ -30489,7 +30492,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>144</v>
@@ -30575,7 +30578,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30661,7 +30664,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>51</v>
@@ -30747,7 +30750,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30833,7 +30836,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
@@ -30919,7 +30922,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2312</v>
+        <v>5404</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
